--- a/Signup_Automation_Test_Cases.xlsx
+++ b/Signup_Automation_Test_Cases.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sys\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F5DA151-FFB2-4BAC-AE57-988DB4F0A749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29DAF880-CE28-464A-BDBA-7DE4C50586A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Signup" sheetId="1" r:id="rId1"/>
+    <sheet name="Login" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Signup!$A$1:$I$21</definedName>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="163">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -371,13 +372,154 @@
   </si>
   <si>
     <t>Success confirmation should be displayed and user should be logged in/redirected to the expected account page</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_AUTO_001</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_AUTO_002</t>
+  </si>
+  <si>
+    <t>Login with valid registered credentials</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_AUTO_003</t>
+  </si>
+  <si>
+    <t>Login with invalid email and valid password</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_AUTO_004</t>
+  </si>
+  <si>
+    <t>Login with valid email and invalid password</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_AUTO_005</t>
+  </si>
+  <si>
+    <t>Login with invalid email and invalid password</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_AUTO_006</t>
+  </si>
+  <si>
+    <t>Verify Email field is mandatory</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_AUTO_007</t>
+  </si>
+  <si>
+    <t>Verify Password field is mandatory</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_AUTO_008</t>
+  </si>
+  <si>
+    <t>Verify login with both fields blank</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_AUTO_009</t>
+  </si>
+  <si>
+    <t>Verify invalid email format validation</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_AUTO_010</t>
+  </si>
+  <si>
+    <t>Verify login after logout</t>
+  </si>
+  <si>
+    <t>Verify successful login displays logged-in user state</t>
+  </si>
+  <si>
+    <t>Enter registered email and valid password and click Login</t>
+  </si>
+  <si>
+    <t>Valid registered email and password</t>
+  </si>
+  <si>
+    <t>User should be logged in successfully and expected logged-in user state should be displayed</t>
+  </si>
+  <si>
+    <t>Enter an unregistered email and valid password and click Login</t>
+  </si>
+  <si>
+    <t>Invalid email + valid password</t>
+  </si>
+  <si>
+    <t>Appropriate login error message should be displayed and user should not be logged in</t>
+  </si>
+  <si>
+    <t>Enter registered email and incorrect password and click Login</t>
+  </si>
+  <si>
+    <t>Valid email + invalid password</t>
+  </si>
+  <si>
+    <t>Enter invalid email and invalid password and click Login</t>
+  </si>
+  <si>
+    <t>Invalid email + invalid password</t>
+  </si>
+  <si>
+    <t>Leave Email blank, enter valid password and click Login</t>
+  </si>
+  <si>
+    <t>Email: Blank; Valid password</t>
+  </si>
+  <si>
+    <t>Required-field validation should be displayed and login should not proceed</t>
+  </si>
+  <si>
+    <t>Enter valid email, leave Password blank and click Login</t>
+  </si>
+  <si>
+    <t>Valid email; Password: Blank</t>
+  </si>
+  <si>
+    <t>Leave Email and Password blank and click Login</t>
+  </si>
+  <si>
+    <t>Email: Blank; Password: Blank</t>
+  </si>
+  <si>
+    <t>Enter invalid email format and valid password and click Login</t>
+  </si>
+  <si>
+    <t>Email: invalid-email; Valid password</t>
+  </si>
+  <si>
+    <t>Invalid email validation should be displayed and login should not proceed</t>
+  </si>
+  <si>
+    <t>Enter a password in the Password field</t>
+  </si>
+  <si>
+    <t>Login successfully, click Logout, and login again using valid credentials</t>
+  </si>
+  <si>
+    <t>User should be able to log in successfully after logout</t>
+  </si>
+  <si>
+    <t>Login using valid credentials and verify the resulting page/account state</t>
+  </si>
+  <si>
+    <t>Success message or logged-in user state should be displayed and expected account options should be available</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_AUTO_011</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -389,6 +531,20 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -426,7 +582,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -436,6 +592,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -739,7 +898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22" style="3" customWidth="1"/>
@@ -1363,9 +1522,515 @@
         <v>17</v>
       </c>
     </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I21" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <mergeCells count="1">
+    <mergeCell ref="A22:I22"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C9D6CF3-800C-4D03-8976-ABF3F997FA35}">
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20" style="3" customWidth="1"/>
+    <col min="3" max="3" width="42" style="3" customWidth="1"/>
+    <col min="4" max="4" width="65" style="3" customWidth="1"/>
+    <col min="5" max="5" width="38" style="3" customWidth="1"/>
+    <col min="6" max="6" width="65" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14" style="3" customWidth="1"/>
+    <col min="8" max="8" width="18" style="3" customWidth="1"/>
+    <col min="9" max="9" width="16" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="8.7265625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Signup_Automation_Test_Cases.xlsx
+++ b/Signup_Automation_Test_Cases.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sys\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29DAF880-CE28-464A-BDBA-7DE4C50586A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{106AB0D5-DF70-40E1-9142-AF7A264F06C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Signup" sheetId="1" r:id="rId1"/>
     <sheet name="Login" sheetId="2" r:id="rId2"/>
+    <sheet name="Product" sheetId="3" r:id="rId3"/>
+    <sheet name="Cart" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Signup!$A$1:$I$21</definedName>
@@ -24,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="320">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -513,6 +515,569 @@
   </si>
   <si>
     <t>TC_LOGIN_AUTO_011</t>
+  </si>
+  <si>
+    <t>TC_PRODUCT_AUTO_001</t>
+  </si>
+  <si>
+    <t>Products</t>
+  </si>
+  <si>
+    <t>Verify Products page is accessible</t>
+  </si>
+  <si>
+    <t>Open Automation Exercise and click the Products button</t>
+  </si>
+  <si>
+    <t>Products page should load successfully and the product listing should be displayed</t>
+  </si>
+  <si>
+    <t>TC_PRODUCT_AUTO_002</t>
+  </si>
+  <si>
+    <t>Verify all products are displayed with product names</t>
+  </si>
+  <si>
+    <t>Navigate to Products page and retrieve the names of all displayed products</t>
+  </si>
+  <si>
+    <t>Available products</t>
+  </si>
+  <si>
+    <t>All available products should be displayed with valid product names</t>
+  </si>
+  <si>
+    <t>TC_PRODUCT_AUTO_003</t>
+  </si>
+  <si>
+    <t>Verify product search functionality</t>
+  </si>
+  <si>
+    <t>Navigate to Products page, enter a valid product name in the search field and click Search</t>
+  </si>
+  <si>
+    <t>Valid product name</t>
+  </si>
+  <si>
+    <t>Search results should be displayed and should contain the searched product</t>
+  </si>
+  <si>
+    <t>TC_PRODUCT_AUTO_004</t>
+  </si>
+  <si>
+    <t>Verify searched product matches the selected product</t>
+  </si>
+  <si>
+    <t>Search for a product and verify the product name displayed in the search results</t>
+  </si>
+  <si>
+    <t>The displayed search result should match the searched product</t>
+  </si>
+  <si>
+    <t>Validation</t>
+  </si>
+  <si>
+    <t>TC_PRODUCT_AUTO_005</t>
+  </si>
+  <si>
+    <t>Verify three different products can be searched sequentially</t>
+  </si>
+  <si>
+    <t>Retrieve product names, select any three products, search for each product one by one and verify the result</t>
+  </si>
+  <si>
+    <t>Three valid product names</t>
+  </si>
+  <si>
+    <t>Each searched product should be displayed correctly in the search results</t>
+  </si>
+  <si>
+    <t>TC_PRODUCT_AUTO_006</t>
+  </si>
+  <si>
+    <t>Verify Add to Cart for the first searched product</t>
+  </si>
+  <si>
+    <t>Search for the first product, verify it, click Add to Cart and observe the result</t>
+  </si>
+  <si>
+    <t>Product 1</t>
+  </si>
+  <si>
+    <t>Product should be added to cart and the appropriate success message should be displayed</t>
+  </si>
+  <si>
+    <t>TC_PRODUCT_AUTO_007</t>
+  </si>
+  <si>
+    <t>Verify Add to Cart for the second searched product</t>
+  </si>
+  <si>
+    <t>Search for the second product, verify it, click Add to Cart and observe the result</t>
+  </si>
+  <si>
+    <t>Product 2</t>
+  </si>
+  <si>
+    <t>TC_PRODUCT_AUTO_008</t>
+  </si>
+  <si>
+    <t>Verify Add to Cart for the third searched product</t>
+  </si>
+  <si>
+    <t>Search for the third product, verify it, click Add to Cart and observe the result</t>
+  </si>
+  <si>
+    <t>Product 3</t>
+  </si>
+  <si>
+    <t>TC_PRODUCT_AUTO_009</t>
+  </si>
+  <si>
+    <t>Verify success message after adding each product to cart</t>
+  </si>
+  <si>
+    <t>Search and add three different products one by one and verify the success message after each addition</t>
+  </si>
+  <si>
+    <t>Product 1, Product 2, Product 3</t>
+  </si>
+  <si>
+    <t>Appropriate success message should be displayed after each product is added to cart</t>
+  </si>
+  <si>
+    <t>TC_PRODUCT_AUTO_010</t>
+  </si>
+  <si>
+    <t>Verify Continue Shopping functionality after adding product</t>
+  </si>
+  <si>
+    <t>Add a product to cart, verify the success message, and click Continue Shopping</t>
+  </si>
+  <si>
+    <t>Valid product</t>
+  </si>
+  <si>
+    <t>User should be returned to the Products page and should be able to continue browsing</t>
+  </si>
+  <si>
+    <t>TC_PRODUCT_AUTO_011</t>
+  </si>
+  <si>
+    <t>Verify multiple products can be added sequentially</t>
+  </si>
+  <si>
+    <t>Search for three different products and add each product to the cart using Continue Shopping between additions</t>
+  </si>
+  <si>
+    <t>Each selected product should be added successfully without interrupting the workflow</t>
+  </si>
+  <si>
+    <t>TC_PRODUCT_AUTO_012</t>
+  </si>
+  <si>
+    <t>Verify complete product search and add-to-cart workflow</t>
+  </si>
+  <si>
+    <t>Open Products → retrieve product names → search three products sequentially → verify each product → Add to Cart → verify success message → Continue Shopping</t>
+  </si>
+  <si>
+    <t>All three products should be successfully added to the cart and the user should be able to continue shopping after each addition</t>
+  </si>
+  <si>
+    <t>TC_CART_AUTO_017</t>
+  </si>
+  <si>
+    <t>Cart</t>
+  </si>
+  <si>
+    <t>Verify guest user can add a product to cart and is prompted to login when proceeding to checkout</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Open the application without logging in.2. Navigate to Products.3. Select any product.4. Add the product to Cart.5. Click Cart.6. Click </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Proceed To Checkout</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Product should be added to the cart successfully. When the guest user clicks Proceed To Checkout, a message prompting the user to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Register/Login to proceed to checkout</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> should be displayed.</t>
+    </r>
+  </si>
+  <si>
+    <t>Negative / Functional</t>
+  </si>
+  <si>
+    <t>TC_CART_AUTO_018</t>
+  </si>
+  <si>
+    <t>Cart/Login</t>
+  </si>
+  <si>
+    <t>Verify guest user can navigate to Login page from checkout login prompt</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Add a product to Cart without logging in.2. Click Proceed To Checkout.3. Verify the login/register prompt.4. Click the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Register/Login</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> link.</t>
+    </r>
+  </si>
+  <si>
+    <t>Clicking the link should navigate the user to the Login/Register page.</t>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>TC_CART_AUTO_019</t>
+  </si>
+  <si>
+    <t>Verify cart products are retained after guest user logs in</t>
+  </si>
+  <si>
+    <t>1. Open application without logging in.2. Add a product to Cart.3. Click Proceed To Checkout.4. Click the Register/Login link.5. Login with valid credentials.6. Navigate to Cart.7. Verify the previously added product.</t>
+  </si>
+  <si>
+    <t>Valid product + valid user credentials</t>
+  </si>
+  <si>
+    <t>User should be logged in successfully and the product added before login should remain in the Cart with the correct product details.</t>
+  </si>
+  <si>
+    <t>TC_CART_AUTO_020</t>
+  </si>
+  <si>
+    <t>Cart/Checkout</t>
+  </si>
+  <si>
+    <t>Verify guest cart is retained and checkout can proceed after login</t>
+  </si>
+  <si>
+    <t>1. Add a product without logging in.2. Go to Cart.3. Click Proceed To Checkout.4. Click Register/Login.5. Login with valid credentials.6. Navigate to Cart.7. Verify previously added product.8. Proceed to Checkout.</t>
+  </si>
+  <si>
+    <t>Previously added product should remain in the cart and the logged-in user should be able to proceed to the Checkout page.</t>
+  </si>
+  <si>
+    <t>TC_CART_AUTO_001</t>
+  </si>
+  <si>
+    <t>Verify cart is empty for a newly logged-in user</t>
+  </si>
+  <si>
+    <t>1. Login with valid credentials.2. Click Cart.3. Verify cart contents.</t>
+  </si>
+  <si>
+    <t>Valid registered user credentials</t>
+  </si>
+  <si>
+    <t>Cart page should be displayed and no products should be present. Empty cart message should be displayed.</t>
+  </si>
+  <si>
+    <t>TC_CART_AUTO_002</t>
+  </si>
+  <si>
+    <t>Verify navigation to Products page from empty cart</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Login.2. Navigate to Cart.3. Verify cart is empty.4. Click </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>here</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> link.</t>
+    </r>
+  </si>
+  <si>
+    <t>Valid user credentials</t>
+  </si>
+  <si>
+    <t>User should be redirected to the Products page and product listings should be displayed.</t>
+  </si>
+  <si>
+    <t>TC_CART_AUTO_003</t>
+  </si>
+  <si>
+    <t>Verify three products can be added to cart</t>
+  </si>
+  <si>
+    <t>1. Navigate to Products.2. Retrieve product names.3. Select any three products.4. Search each product one by one.5. Verify searched product.6. Add each product to cart.7. Verify success message after each addition.8. Click Continue Shopping.</t>
+  </si>
+  <si>
+    <t>All three selected products should be added successfully and success message should be displayed after each addition.</t>
+  </si>
+  <si>
+    <t>TC_CART_AUTO_004</t>
+  </si>
+  <si>
+    <t>Verify added product details in cart</t>
+  </si>
+  <si>
+    <t>1. Add three products.2. Click Cart.3. Capture product name, price and quantity.4. Compare with stored product details.</t>
+  </si>
+  <si>
+    <t>Three valid products</t>
+  </si>
+  <si>
+    <t>Cart should display the correct product names, prices, quantities and total prices.</t>
+  </si>
+  <si>
+    <t>TC_CART_AUTO_005</t>
+  </si>
+  <si>
+    <t>Verify removing a product from cart</t>
+  </si>
+  <si>
+    <t>1. Add three products.2. Navigate to Cart.3. Select any one product.4. Click Remove/Delete.5. Verify cart contents.</t>
+  </si>
+  <si>
+    <t>Selected product should be removed and the remaining products should still be displayed.</t>
+  </si>
+  <si>
+    <t>TC_CART_AUTO_006</t>
+  </si>
+  <si>
+    <t>Verify quantity when the same product is added multiple times</t>
+  </si>
+  <si>
+    <t>1. Search for a product.2. Add the same product multiple times.3. Navigate to Cart.4. Verify product quantity.</t>
+  </si>
+  <si>
+    <t>Same product added 3 times</t>
+  </si>
+  <si>
+    <t>Product should be present in the cart with the correct quantity/count.</t>
+  </si>
+  <si>
+    <t>TC_CART_AUTO_007</t>
+  </si>
+  <si>
+    <t>Verify cart total calculation</t>
+  </si>
+  <si>
+    <t>1. Add multiple products.2. Navigate to Cart.3. Capture unit price and quantity.4. Calculate expected total.5. Compare with displayed total.</t>
+  </si>
+  <si>
+    <t>Product prices and quantities</t>
+  </si>
+  <si>
+    <t>Displayed total should match the calculated total based on price × quantity.</t>
+  </si>
+  <si>
+    <t>TC_CART_AUTO_008</t>
+  </si>
+  <si>
+    <t>Checkout</t>
+  </si>
+  <si>
+    <t>Verify checkout page details</t>
+  </si>
+  <si>
+    <t>1. Add products.2. Navigate to Cart.3. Click Proceed To Checkout.4. Verify delivery address.5. Verify billing address.6. Verify order details.</t>
+  </si>
+  <si>
+    <t>Logged-in user with saved address</t>
+  </si>
+  <si>
+    <t>Checkout page should display correct customer address, products, quantities, prices and total amount.</t>
+  </si>
+  <si>
+    <t>TC_CART_AUTO_009</t>
+  </si>
+  <si>
+    <t>Verify order placement with valid payment details</t>
+  </si>
+  <si>
+    <t>1. Navigate to Checkout.2. Click Place Order.3. Enter valid test card details.4. Click Pay and Confirm Order.</t>
+  </si>
+  <si>
+    <t>Dummy/test payment data</t>
+  </si>
+  <si>
+    <t>Order should be processed successfully.</t>
+  </si>
+  <si>
+    <t>TC_CART_AUTO_010</t>
+  </si>
+  <si>
+    <t>Verify successful order message and Continue button</t>
+  </si>
+  <si>
+    <t>1. Complete the order.2. Verify order confirmation message.3. Click Continue.</t>
+  </si>
+  <si>
+    <t>Successfully placed order</t>
+  </si>
+  <si>
+    <t>Order success message should be displayed and Continue button should navigate to the expected page.</t>
+  </si>
+  <si>
+    <t>TC_CART_AUTO_011</t>
+  </si>
+  <si>
+    <t>Verify checkout cannot proceed with an empty cart</t>
+  </si>
+  <si>
+    <t>1. Login.2. Navigate to Cart.3. Ensure cart is empty.4. Attempt to proceed to checkout.</t>
+  </si>
+  <si>
+    <t>Empty cart</t>
+  </si>
+  <si>
+    <t>User should not be able to place an order without products in the cart.</t>
+  </si>
+  <si>
+    <t>TC_CART_AUTO_012</t>
+  </si>
+  <si>
+    <t>Verify payment form validation with empty fields</t>
+  </si>
+  <si>
+    <t>1. Add a product.2. Navigate to Checkout.3. Click Place Order.4. Leave payment fields empty.5. Attempt to submit payment.</t>
+  </si>
+  <si>
+    <t>Empty payment fields</t>
+  </si>
+  <si>
+    <t>Appropriate validation should be displayed and order should not be completed, if validation is implemented.</t>
+  </si>
+  <si>
+    <t>TC_CART_AUTO_013</t>
+  </si>
+  <si>
+    <t>Verify payment form handling with invalid details</t>
+  </si>
+  <si>
+    <t>1. Add a product.2. Navigate to Checkout.3. Click Place Order.4. Enter invalid payment details.5. Submit payment.</t>
+  </si>
+  <si>
+    <t>Invalid card/test payment data</t>
+  </si>
+  <si>
+    <t>Invalid payment data should be rejected or handled according to the application's validation rules.</t>
+  </si>
+  <si>
+    <t>TC_CART_AUTO_014</t>
+  </si>
+  <si>
+    <t>Verify removed product is not present during checkout</t>
+  </si>
+  <si>
+    <t>1. Add three products.2. Remove one product from Cart.3. Click Checkout.4. Verify order summary.</t>
+  </si>
+  <si>
+    <t>Three products; one removed</t>
+  </si>
+  <si>
+    <t>Removed product should not appear in the checkout order summary and total should be recalculated.</t>
+  </si>
+  <si>
+    <t>TC_CART_AUTO_015</t>
+  </si>
+  <si>
+    <t>Verify cart contents persist when navigating between Cart and Products</t>
+  </si>
+  <si>
+    <t>1. Add products to cart.2. Open Cart.3. Click Continue Shopping.4. Return to Cart.5. Verify products.</t>
+  </si>
+  <si>
+    <t>Two or more products</t>
+  </si>
+  <si>
+    <t>Previously added products should remain in the cart with correct quantities.</t>
+  </si>
+  <si>
+    <t>TC_CART_AUTO_016</t>
+  </si>
+  <si>
+    <t>Verify complete Cart to Order workflow</t>
+  </si>
+  <si>
+    <t>1. Login.2. Verify empty Cart.3. Navigate to Products.4. Add three products.5. Verify Cart details.6. Remove one product.7. Add a product multiple times.8. Verify quantity.9. Proceed to Checkout.10. Verify order details.11. Place order using test payment data.12. Verify success page.13. Click Continue.</t>
+  </si>
+  <si>
+    <t>Valid user, three products, dummy payment data</t>
+  </si>
+  <si>
+    <t>Complete Cart → Checkout → Order workflow should execute successfully and order confirmation should be displayed.</t>
   </si>
 </sst>
 </file>
@@ -582,7 +1147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -593,8 +1158,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1523,15 +2110,15 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="2"/>
@@ -2033,4 +2620,1028 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E837262E-2F8F-4A48-AC22-1EE9C3DACA60}">
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="26.36328125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="13" style="7" customWidth="1"/>
+    <col min="3" max="3" width="26.6328125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="24.7265625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="29" style="7" customWidth="1"/>
+    <col min="6" max="6" width="34.26953125" style="8" customWidth="1"/>
+    <col min="7" max="7" width="17.08984375" style="7" customWidth="1"/>
+    <col min="8" max="8" width="19.08984375" style="7" customWidth="1"/>
+    <col min="9" max="9" width="19.1796875" style="7" customWidth="1"/>
+    <col min="10" max="16384" width="8.7265625" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06DAA2FB-30BE-4F18-B8BD-2BF5A16BCC88}">
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.6328125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="20.26953125" customWidth="1"/>
+    <col min="3" max="3" width="24.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="232" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="232" x14ac:dyDescent="0.35">
+      <c r="A5" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="261" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="261" x14ac:dyDescent="0.35">
+      <c r="A9" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="203" x14ac:dyDescent="0.35">
+      <c r="A11" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="232" x14ac:dyDescent="0.35">
+      <c r="A13" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="391.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="261" x14ac:dyDescent="0.35">
+      <c r="A19" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>